--- a/data/cox_xlsx/BIOPOR.CO.xlsx
+++ b/data/cox_xlsx/BIOPOR.CO.xlsx
@@ -9614,7 +9614,9 @@
       <c r="A45" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="B45" s="16"/>
+      <c r="B45" s="15">
+        <v>3.37</v>
+      </c>
       <c r="C45" s="15">
         <v>1.38</v>
       </c>
